--- a/artfynd/A 27625-2023 artfynd.xlsx
+++ b/artfynd/A 27625-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27625-2023 artfynd.xlsx
+++ b/artfynd/A 27625-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118237611</v>
+        <v>118237497</v>
       </c>
       <c r="B3" t="n">
-        <v>57309</v>
+        <v>100107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,46 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657557</v>
+        <v>657487</v>
       </c>
       <c r="R3" t="n">
-        <v>6642095</v>
+        <v>6642073</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1009,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118237497</v>
+        <v>118237611</v>
       </c>
       <c r="B5" t="n">
-        <v>100107</v>
+        <v>57309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,37 +1016,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>657487</v>
+        <v>657557</v>
       </c>
       <c r="R5" t="n">
-        <v>6642073</v>
+        <v>6642095</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 27625-2023 artfynd.xlsx
+++ b/artfynd/A 27625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110257610</v>
+        <v>118237555</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657535.1638611336</v>
+        <v>657446</v>
       </c>
       <c r="R2" t="n">
-        <v>6642102.630238112</v>
+        <v>6641809</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118237497</v>
+        <v>110257610</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657487</v>
+        <v>657535</v>
       </c>
       <c r="R3" t="n">
-        <v>6642073</v>
+        <v>6642103</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,16 +886,11 @@
         <v>118237606</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1003,12 +992,7 @@
         <v>118237611</v>
       </c>
       <c r="B5" t="n">
-        <v>57309</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,12 +1098,7 @@
         <v>118237489</v>
       </c>
       <c r="B6" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,6 +1193,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118237497</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>657487</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6642073</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
